--- a/documents/김진아/졸작 계획서_김진아.xlsx
+++ b/documents/김진아/졸작 계획서_김진아.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A0FC35-7BD8-40A7-BAE4-9BEFF0A1BA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6BF1E0-75DD-42B6-BA24-FAC98BFF6147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="36">
   <si>
     <t xml:space="preserve"> 시작 날짜:</t>
   </si>
@@ -51,35 +51,7 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>게임 ai 및 state tree 개념 조사, 학습</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>state tree 기반 ai 프로토타입 제작</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>EQS 학습 및 프로토타입 제작</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>학습 내용 복습 및 정리</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>state tree,EQS 시스템 연동</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">           몬스터 AI 기능 구현</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 AI 기능 구현</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>전투 AI 구현 및 테스트</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
@@ -135,30 +107,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>몬스터 AI 기능 구현</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>전투 AI 기능 구현 및 개선</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>보스 AI 구현</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>보스 AI 및 몬스터 AI 기능 구현</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>보스 AI 및 몬스터 기능 구현</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터, 보스 상호작용 시스템 구현</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>전체 통합 및 완성, 5월부터 디버깅 및 최적화</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -175,11 +123,59 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>state tree 기반 AI 프로토타입 제작</t>
+    <t>토</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>토</t>
+    <t>선행연구 분석 및 언리얼 ai 기능 학습</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>언리얼 AI 시스템 학습</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 몬스터 AI 구현</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>생태계 AI 시스템 구현</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">           몬스터, 화물 상호작용 구현</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 , 화물 상호작용 및 프로토타입 제작</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로토타입 테스트</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>미래 예측 시스템 알고리즘 학습 및 구현</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>경로 시간 예측 시스템 구현</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 알고리즘 개선</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 시스템 최적화 및 테스트</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 시스템 통합 및 확장,테스트</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 시스템 통합 및 확장, 테스트</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -828,7 +824,7 @@
     <xf numFmtId="0" fontId="1" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -895,6 +891,18 @@
     <xf numFmtId="0" fontId="21" fillId="46" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="1" xfId="6" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -907,23 +915,17 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="41" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="1" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -1329,48 +1331,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:30" ht="48.75" customHeight="1">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
     </row>
     <row r="2" spans="2:30" ht="24.75" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="23">
         <f>DATEVALUE("2026/09/01")</f>
         <v>46266</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
     </row>
     <row r="3" spans="2:30" ht="12.75" customHeight="1"/>
     <row r="4" spans="2:30" ht="18.75" customHeight="1">
@@ -1722,40 +1724,40 @@
     </row>
     <row r="7" spans="2:30" ht="30" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y7" s="26"/>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="26"/>
-      <c r="AC7" s="26"/>
-      <c r="AD7" s="26"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="25"/>
     </row>
     <row r="8" spans="2:30" ht="30" customHeight="1">
       <c r="B8" s="13"/>
@@ -2104,40 +2106,40 @@
     </row>
     <row r="11" spans="2:30" ht="30" customHeight="1">
       <c r="B11" s="13"/>
-      <c r="C11" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="22"/>
+      <c r="C11" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="26"/>
+      <c r="Z11" s="26"/>
+      <c r="AA11" s="26"/>
+      <c r="AB11" s="26"/>
+      <c r="AC11" s="26"/>
+      <c r="AD11" s="26"/>
     </row>
     <row r="12" spans="2:30" ht="30" customHeight="1">
       <c r="B12" s="13"/>
@@ -2486,40 +2488,40 @@
     </row>
     <row r="15" spans="2:30" ht="30" customHeight="1">
       <c r="B15" s="13"/>
-      <c r="C15" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="31"/>
-      <c r="AA15" s="31"/>
-      <c r="AB15" s="31"/>
-      <c r="AC15" s="31"/>
-      <c r="AD15" s="31"/>
+      <c r="C15" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="30"/>
+      <c r="AA15" s="30"/>
+      <c r="AB15" s="30"/>
+      <c r="AC15" s="30"/>
+      <c r="AD15" s="30"/>
     </row>
     <row r="16" spans="2:30" ht="30" customHeight="1">
       <c r="B16" s="13"/>
@@ -2868,26 +2870,26 @@
     </row>
     <row r="19" spans="2:30" ht="30" customHeight="1">
       <c r="B19" s="13"/>
-      <c r="C19" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
+      <c r="C19" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
       <c r="S19" s="15" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="T19" s="15"/>
       <c r="U19" s="15"/>
@@ -2895,13 +2897,13 @@
       <c r="W19" s="15"/>
       <c r="X19" s="15"/>
       <c r="Y19" s="15"/>
-      <c r="Z19" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA19" s="24"/>
-      <c r="AB19" s="24"/>
-      <c r="AC19" s="24"/>
-      <c r="AD19" s="24"/>
+      <c r="Z19" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="28"/>
+      <c r="AC19" s="28"/>
+      <c r="AD19" s="28"/>
     </row>
     <row r="20" spans="2:30" ht="30" customHeight="1">
       <c r="B20" s="13"/>
@@ -2934,7 +2936,7 @@
         <v/>
       </c>
       <c r="J20" s="8" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K20" s="8" t="str">
         <f t="shared" ref="K20" si="158">IF(TEXT(K22,"m월")=TEXT(J22,"m월"),"",LOWER(TEXT(K22,"m월")))</f>
@@ -3248,7 +3250,7 @@
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
@@ -3261,10 +3263,10 @@
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
       <c r="P23" s="17" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
+      <c r="R23" s="32"/>
       <c r="S23" s="17"/>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
@@ -3275,7 +3277,7 @@
       <c r="Z23" s="16"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="16" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AC23" s="16"/>
       <c r="AD23" s="16"/>
@@ -3329,10 +3331,10 @@
         <v/>
       </c>
       <c r="P24" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="R24" s="7" t="str">
         <f t="shared" ref="R24" si="207">IF(TEXT(R26,"m월")=TEXT(Q26,"m월"),"",LOWER(TEXT(R26,"m월")))</f>
@@ -3359,7 +3361,7 @@
         <v/>
       </c>
       <c r="X24" s="8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y24" s="8" t="str">
         <f t="shared" ref="Y24" si="212">IF(TEXT(Y26,"m월")=TEXT(X26,"m월"),"",LOWER(TEXT(Y26,"m월")))</f>
@@ -3389,88 +3391,88 @@
     <row r="25" spans="2:30" ht="30" customHeight="1">
       <c r="B25" s="13"/>
       <c r="C25" s="9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="O25" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="P25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="T25" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="U25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="V25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="W25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="X25" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y25" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z25" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="Q25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="R25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="S25" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T25" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="U25" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="V25" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="W25" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="X25" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z25" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA25" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB25" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="AC25" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AD25" s="10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="2:30" ht="30" customHeight="1" thickBot="1">
@@ -3567,10 +3569,10 @@
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
       <c r="G27" s="16" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
+      <c r="I27" s="33"/>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
       <c r="L27" s="19"/>
@@ -3578,7 +3580,7 @@
       <c r="N27" s="19"/>
       <c r="O27" s="19"/>
       <c r="P27" s="19" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q27" s="19"/>
       <c r="R27" s="19"/>
@@ -3591,7 +3593,7 @@
       <c r="Y27" s="20"/>
       <c r="Z27" s="20"/>
       <c r="AA27" s="20" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="AB27" s="20"/>
       <c r="AC27" s="20"/>
@@ -3600,7 +3602,7 @@
     <row r="28" spans="2:30" ht="30" customHeight="1">
       <c r="B28" s="13"/>
       <c r="C28" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D28" s="7" t="str">
         <f t="shared" ref="D28" si="218">IF(TEXT(D30,"m월")=TEXT(C30,"m월"),"",LOWER(TEXT(D30,"m월")))</f>
@@ -3627,7 +3629,7 @@
         <v/>
       </c>
       <c r="J28" s="8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K28" s="8" t="str">
         <f t="shared" ref="K28" si="223">IF(TEXT(K30,"m월")=TEXT(J30,"m월"),"",LOWER(TEXT(K30,"m월")))</f>
@@ -3647,10 +3649,10 @@
         <v/>
       </c>
       <c r="P28" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R28" s="7" t="str">
         <f t="shared" ref="R28" si="227">IF(TEXT(R30,"m월")=TEXT(Q30,"m월"),"",LOWER(TEXT(R30,"m월")))</f>
@@ -3677,7 +3679,7 @@
         <v/>
       </c>
       <c r="X28" s="8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Y28" s="8" t="str">
         <f t="shared" ref="Y28" si="232">IF(TEXT(Y30,"m월")=TEXT(X30,"m월"),"",LOWER(TEXT(Y30,"m월")))</f>
@@ -3707,88 +3709,88 @@
     <row r="29" spans="2:30" ht="30" customHeight="1">
       <c r="B29" s="13"/>
       <c r="C29" s="9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I29" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="O29" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="P29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="T29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="U29" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="R29" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="S29" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T29" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="U29" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="V29" s="9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W29" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="X29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y29" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z29" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="X29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y29" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z29" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA29" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB29" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="AC29" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AD29" s="10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="2:30" ht="30" customHeight="1">
@@ -3883,7 +3885,7 @@
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
       <c r="E31" s="20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F31" s="20"/>
       <c r="G31" s="20"/>
@@ -3898,7 +3900,7 @@
       <c r="P31" s="21"/>
       <c r="Q31" s="21"/>
       <c r="R31" s="21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S31" s="21"/>
       <c r="T31" s="21"/>
@@ -3916,7 +3918,7 @@
     <row r="32" spans="2:30" ht="30" customHeight="1">
       <c r="B32" s="13"/>
       <c r="C32" s="6" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D32" s="7" t="str">
         <f t="shared" ref="D32" si="238">IF(TEXT(D34,"m월")=TEXT(C34,"m월"),"",LOWER(TEXT(D34,"m월")))</f>
@@ -3943,7 +3945,7 @@
         <v/>
       </c>
       <c r="J32" s="8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K32" s="8" t="str">
         <f t="shared" ref="K32" si="243">IF(TEXT(K34,"m월")=TEXT(J34,"m월"),"",LOWER(TEXT(K34,"m월")))</f>
@@ -3972,7 +3974,7 @@
         <v/>
       </c>
       <c r="S32" s="7" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="T32" s="7" t="str">
         <f t="shared" ref="T32" si="248">IF(TEXT(T34,"m월")=TEXT(S34,"m월"),"",LOWER(TEXT(T34,"m월")))</f>
@@ -3991,7 +3993,7 @@
         <v/>
       </c>
       <c r="X32" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Y32" s="8" t="str">
         <f t="shared" ref="Y32" si="252">IF(TEXT(Y34,"m월")=TEXT(X34,"m월"),"",LOWER(TEXT(Y34,"m월")))</f>
@@ -4021,88 +4023,88 @@
     <row r="33" spans="2:30" ht="30" customHeight="1">
       <c r="B33" s="13"/>
       <c r="C33" s="9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I33" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J33" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="O33" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="P33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R33" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="S33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="T33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="U33" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="R33" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="S33" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T33" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="U33" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="V33" s="9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W33" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="X33" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y33" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z33" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="X33" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y33" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z33" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA33" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB33" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="AC33" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AD33" s="10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="2:30" ht="30" customHeight="1">
@@ -4199,7 +4201,7 @@
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
       <c r="G35" s="21" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H35" s="21"/>
       <c r="I35" s="21"/>
@@ -4217,7 +4219,7 @@
       <c r="U35" s="20"/>
       <c r="V35" s="20"/>
       <c r="W35" s="20" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="X35" s="20"/>
       <c r="Y35" s="20"/>
@@ -4229,12 +4231,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B1:AD1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="X7:AD7"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="J7:W7"/>
     <mergeCell ref="Z19:AD19"/>
     <mergeCell ref="J15:W15"/>
     <mergeCell ref="X15:AD15"/>
@@ -4242,6 +4238,12 @@
     <mergeCell ref="C11:I11"/>
     <mergeCell ref="X11:AD11"/>
     <mergeCell ref="J11:W11"/>
+    <mergeCell ref="B1:AD1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="X7:AD7"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="J7:W7"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <conditionalFormatting sqref="C5:AD6">
